--- a/plugins/fire-service/skills/eptz/assets/smetka_template.xlsx
+++ b/plugins/fire-service/skills/eptz/assets/smetka_template.xlsx
@@ -804,7 +804,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:F47"/>
   <sheetFormatPr defaultColWidth="9.13671875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -828,7 +828,7 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" s="3" customFormat="true" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" s="3" customFormat="true" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>

--- a/plugins/fire-service/skills/eptz/assets/smetka_template.xlsx
+++ b/plugins/fire-service/skills/eptz/assets/smetka_template.xlsx
@@ -126,7 +126,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -190,6 +190,7 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -201,7 +202,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -447,6 +448,10 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -525,6 +530,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>142875</colOff>
+      <row>1</row>
+      <rowOff>38100</rowOff>
+    </from>
+    <ext cx="6467475" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -658,39 +693,13 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customFormat="1" customHeight="1" s="43">
-      <c r="A2" s="45" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">МИНИСТЕРСТВО НА ВЪТРЕШНИТЕ РАБОТИ
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">ГЛАВНА ДИРЕКЦИЯ „ПОЖАРНА БЕЗОПАСНОСТ И ЗАЩИТА НА НАСЕЛЕНИЕТО”
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <sz val="10.5"/>
-            </rPr>
-            <t>РЕГИОНАЛНА ДИРЕКЦИЯ „ПОЖАРНА БЕЗОПАСНОСТ И ЗАЩИТА НА НАСЕЛЕНИЕТО” – ПЛЕВЕН</t>
-          </r>
-        </is>
-      </c>
-      <c r="B2" s="46" t="n"/>
-      <c r="C2" s="46" t="n"/>
-      <c r="D2" s="46" t="n"/>
-      <c r="E2" s="46" t="n"/>
-      <c r="F2" s="46" t="n"/>
+    <row r="2" ht="66" customFormat="1" customHeight="1" s="43">
+      <c r="A2" s="85" t="n"/>
+      <c r="B2" s="86" t="n"/>
+      <c r="C2" s="86" t="n"/>
+      <c r="D2" s="86" t="n"/>
+      <c r="E2" s="86" t="n"/>
+      <c r="F2" s="86" t="n"/>
     </row>
     <row r="3" ht="7.5" customFormat="1" customHeight="1" s="43">
       <c r="A3" s="47" t="n"/>
@@ -1150,51 +1159,7 @@
     <row r="31" ht="30" customHeight="1" s="51">
       <c r="A31" s="77" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <charset val="204"/>
-              <family val="1"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">         Сумата да бъде преведена по сметка с IBAN № </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <charset val="204"/>
-              <family val="1"/>
-              <sz val="12"/>
-            </rPr>
-            <t>BG96UBBS80023112509310</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <charset val="204"/>
-              <family val="1"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">, при банка </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <charset val="204"/>
-              <family val="1"/>
-              <sz val="12"/>
-            </rPr>
-            <t>ОББ-АД – клон Плевен</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <charset val="204"/>
-              <family val="1"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve"> в 30 дневен срок от датата на приемането на експертизата.</t>
-          </r>
+          <t xml:space="preserve">         Сумата да бъде преведена по сметка с IBAN № BG96UBBS80023112509310, при банка ОББ-АД – клон Плевен в 30 дневен срок от датата на приемането на експертизата.</t>
         </is>
       </c>
     </row>
@@ -1232,48 +1197,14 @@
     <row r="37" ht="12.75" customHeight="1" s="51">
       <c r="A37" s="48" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <charset val="204"/>
-              <family val="1"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">Екз.№3 – Възложител </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <charset val="204"/>
-              <family val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>(без приложение)</t>
-          </r>
+          <t>Екз.№3 – Възложител (без приложение)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="12.75" customHeight="1" s="51">
       <c r="A38" s="48" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <charset val="204"/>
-              <family val="1"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">Екз.№4 – ФО </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <charset val="204"/>
-              <family val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t>(без приложение)</t>
-          </r>
+          <t>Екз.№4 – ФО (без приложение)</t>
         </is>
       </c>
     </row>
@@ -1283,33 +1214,7 @@
     <row r="40" ht="15" customHeight="1" s="51">
       <c r="A40" s="78" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <charset val="204"/>
-              <family val="1"/>
-              <sz val="12"/>
-            </rPr>
-            <t>      </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <charset val="204"/>
-              <family val="1"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">  Приложение:</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <charset val="204"/>
-              <family val="1"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve"> Експертиза – 1 бр.</t>
-          </r>
+          <t xml:space="preserve">        Приложение: Експертиза – 1 бр.</t>
         </is>
       </c>
     </row>
@@ -1432,5 +1337,6 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.39375" right="0.39375" top="0.39375" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/plugins/fire-service/skills/eptz/assets/smetka_template.xlsx
+++ b/plugins/fire-service/skills/eptz/assets/smetka_template.xlsx
@@ -78,6 +78,7 @@
       <name val="Times New Roman"/>
       <charset val="204"/>
       <family val="1"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
@@ -90,6 +91,7 @@
       <name val="Times New Roman"/>
       <charset val="204"/>
       <family val="1"/>
+      <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
@@ -126,7 +128,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -190,7 +192,6 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border/>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -202,7 +203,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -304,6 +305,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -361,27 +365,21 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -396,19 +394,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -448,10 +443,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -530,36 +521,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>142875</colOff>
-      <row>1</row>
-      <rowOff>38100</rowOff>
-    </from>
-    <ext cx="6467475" cy="762000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -677,622 +638,749 @@
   <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.13671875" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="4.41" customWidth="1" style="42" min="1" max="1"/>
-    <col width="45.7" customWidth="1" style="42" min="2" max="2"/>
-    <col width="7.56" customWidth="1" style="42" min="3" max="3"/>
-    <col width="13.85" customWidth="1" style="42" min="4" max="4"/>
-    <col width="11.7" customWidth="1" style="42" min="5" max="5"/>
-    <col width="13.7" customWidth="1" style="42" min="6" max="6"/>
-    <col width="9.140000000000001" customWidth="1" style="42" min="7" max="257"/>
+    <col width="4.41" customWidth="1" style="43" min="1" max="1"/>
+    <col width="45.7" customWidth="1" style="43" min="2" max="2"/>
+    <col width="7.56" customWidth="1" style="43" min="3" max="3"/>
+    <col width="13.85" customWidth="1" style="43" min="4" max="4"/>
+    <col width="11.7" customWidth="1" style="43" min="5" max="5"/>
+    <col width="13.7" customWidth="1" style="43" min="6" max="6"/>
+    <col width="9.140000000000001" customWidth="1" style="43" min="7" max="257"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customFormat="1" customHeight="1" s="43">
-      <c r="A1" s="44" t="inlineStr">
+    <row r="1" ht="15" customFormat="1" customHeight="1" s="44">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>Приложение № 1</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="66" customFormat="1" customHeight="1" s="43">
-      <c r="A2" s="85" t="n"/>
-      <c r="B2" s="86" t="n"/>
-      <c r="C2" s="86" t="n"/>
-      <c r="D2" s="86" t="n"/>
-      <c r="E2" s="86" t="n"/>
-      <c r="F2" s="86" t="n"/>
-    </row>
-    <row r="3" ht="7.5" customFormat="1" customHeight="1" s="43">
-      <c r="A3" s="47" t="n"/>
-      <c r="B3" s="47" t="n"/>
-      <c r="C3" s="47" t="n"/>
-      <c r="D3" s="47" t="n"/>
-      <c r="E3" s="47" t="n"/>
-      <c r="F3" s="47" t="n"/>
-    </row>
-    <row r="4" ht="15" customFormat="1" customHeight="1" s="43">
-      <c r="A4" s="48" t="inlineStr">
-        <is>
-          <t>рег.№ ……………………….</t>
-        </is>
-      </c>
-      <c r="C4" s="47" t="n"/>
-      <c r="D4" s="47" t="n"/>
-      <c r="E4" s="47" t="n"/>
-      <c r="F4" s="47" t="n"/>
-    </row>
-    <row r="5" ht="15" customFormat="1" customHeight="1" s="43">
-      <c r="A5" s="48" t="inlineStr">
+    <row r="2" ht="52" customFormat="1" customHeight="1" s="44">
+      <c r="A2" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <charset val="204"/>
+              <family val="1"/>
+              <sz val="16"/>
+            </rPr>
+            <t xml:space="preserve">МИНИСТЕРСТВО НА ВЪТРЕШНИТЕ РАБОТИ
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <charset val="204"/>
+              <family val="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">ГЛАВНА ДИРЕКЦИЯ „ПОЖАРНА БЕЗОПАСНОСТ И ЗАЩИТА НА НАСЕЛЕНИЕТО”
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <charset val="204"/>
+              <family val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>РЕГИОНАЛНА ДИРЕКЦИЯ „ПОЖАРНА БЕЗОПАСНОСТ И ЗАЩИТА НА НАСЕЛЕНИЕТО” – ПЛЕВЕН</t>
+          </r>
+        </is>
+      </c>
+      <c r="B2" s="47" t="n"/>
+      <c r="C2" s="47" t="n"/>
+      <c r="D2" s="47" t="n"/>
+      <c r="E2" s="47" t="n"/>
+      <c r="F2" s="47" t="n"/>
+    </row>
+    <row r="3" ht="7.5" customFormat="1" customHeight="1" s="44">
+      <c r="A3" s="48" t="n"/>
+      <c r="B3" s="48" t="n"/>
+      <c r="C3" s="48" t="n"/>
+      <c r="D3" s="48" t="n"/>
+      <c r="E3" s="48" t="n"/>
+      <c r="F3" s="48" t="n"/>
+    </row>
+    <row r="4" ht="15" customFormat="1" customHeight="1" s="44">
+      <c r="A4" s="49" t="inlineStr">
+        <is>
+          <t>рег.№ ………………………., екз.№……</t>
+        </is>
+      </c>
+      <c r="C4" s="48" t="n"/>
+      <c r="D4" s="48" t="n"/>
+      <c r="E4" s="48" t="n"/>
+      <c r="F4" s="48" t="n"/>
+    </row>
+    <row r="5" ht="15" customFormat="1" customHeight="1" s="44">
+      <c r="A5" s="49" t="inlineStr">
         <is>
           <t>……………20……г.</t>
         </is>
       </c>
-      <c r="C5" s="47" t="n"/>
-      <c r="D5" s="47" t="n"/>
-      <c r="E5" s="47" t="n"/>
-      <c r="F5" s="47" t="n"/>
-    </row>
-    <row r="6" ht="18" customFormat="1" customHeight="1" s="43">
-      <c r="A6" s="49" t="inlineStr">
+      <c r="C5" s="48" t="n"/>
+      <c r="D5" s="48" t="n"/>
+      <c r="E5" s="48" t="n"/>
+      <c r="F5" s="48" t="n"/>
+    </row>
+    <row r="6" ht="18" customFormat="1" customHeight="1" s="44">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>С М Е Т К А</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="108" customFormat="1" customHeight="1" s="43">
-      <c r="A7" s="50" t="inlineStr">
+    <row r="7" ht="108" customFormat="1" customHeight="1" s="44">
+      <c r="A7" s="51" t="inlineStr">
         <is>
           <t>по чл.23, ал.3 от Наредба № H-1/14.02.2023г. за вписването, квалификацията и възнагражденията на вещите лица за направените разходи за труд, консумативи и режийни разноски по експертиза №………….......................….......…../…….…….............. г., назначена от …………………...…………....…….....…… при ………...........……………... с постановление за назначаване на експертиза по ДП/НОХД/гр.дело/адм.дело/изп.дело № ........................ по описа на  ..................................... извършена от инспектор ........................................................................... – инспектор IV ст. в група ОЦ на сектор ПГ и СД към РДПБЗН – Плевен при ГДПБЗН – МВР</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="7.5" customHeight="1" s="51">
-      <c r="A8" s="52" t="n"/>
-      <c r="B8" s="46" t="n"/>
-      <c r="C8" s="46" t="n"/>
-      <c r="D8" s="46" t="n"/>
-      <c r="E8" s="46" t="n"/>
-      <c r="F8" s="46" t="n"/>
-    </row>
-    <row r="9" ht="15" customFormat="1" customHeight="1" s="53">
-      <c r="A9" s="54" t="inlineStr">
+    <row r="8" ht="7.5" customHeight="1" s="52">
+      <c r="A8" s="53" t="n"/>
+      <c r="B8" s="47" t="n"/>
+      <c r="C8" s="47" t="n"/>
+      <c r="D8" s="47" t="n"/>
+      <c r="E8" s="47" t="n"/>
+      <c r="F8" s="47" t="n"/>
+    </row>
+    <row r="9" ht="15" customFormat="1" customHeight="1" s="54">
+      <c r="A9" s="55" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B9" s="54" t="inlineStr">
+      <c r="B9" s="55" t="inlineStr">
         <is>
           <t>ВИД РАЗХОД</t>
         </is>
       </c>
-      <c r="C9" s="54" t="inlineStr">
+      <c r="C9" s="55" t="inlineStr">
         <is>
           <t>МЯРКА</t>
         </is>
       </c>
-      <c r="D9" s="54" t="inlineStr">
+      <c r="D9" s="55" t="inlineStr">
         <is>
           <t>КОЛИЧЕСТВО</t>
         </is>
       </c>
-      <c r="E9" s="55" t="inlineStr">
+      <c r="E9" s="56" t="inlineStr">
         <is>
           <t>ЕД. ЦЕНА</t>
         </is>
       </c>
-      <c r="F9" s="55" t="inlineStr">
+      <c r="F9" s="56" t="inlineStr">
         <is>
           <t>ОБЩА СУМА</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="12.75" customFormat="1" customHeight="1" s="43">
-      <c r="A10" s="56" t="inlineStr">
+    <row r="10" ht="12.75" customFormat="1" customHeight="1" s="44">
+      <c r="A10" s="57" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
-      <c r="B10" s="57" t="inlineStr">
+      <c r="B10" s="58" t="inlineStr">
         <is>
           <t>Разходи за труд</t>
         </is>
       </c>
-      <c r="C10" s="58" t="n"/>
-      <c r="D10" s="58" t="n"/>
-      <c r="E10" s="59" t="n"/>
-      <c r="F10" s="60" t="n"/>
-    </row>
-    <row r="11" ht="12.75" customFormat="1" customHeight="1" s="43">
-      <c r="A11" s="61" t="inlineStr">
+      <c r="C10" s="59" t="n"/>
+      <c r="D10" s="59" t="n"/>
+      <c r="E10" s="60" t="n"/>
+      <c r="F10" s="61" t="n"/>
+    </row>
+    <row r="11" ht="12.75" customFormat="1" customHeight="1" s="44">
+      <c r="A11" s="58" t="inlineStr">
         <is>
           <t>1.1.</t>
         </is>
       </c>
-      <c r="B11" s="62" t="inlineStr">
+      <c r="B11" s="57" t="inlineStr">
         <is>
           <t>Инспектор VI - IV степен</t>
         </is>
       </c>
-      <c r="C11" s="63" t="inlineStr">
+      <c r="C11" s="62" t="inlineStr">
         <is>
           <t>час</t>
         </is>
       </c>
-      <c r="D11" s="64" t="n">
+      <c r="D11" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="65">
+      <c r="E11" s="64">
         <f>3.5%*620.2</f>
         <v/>
       </c>
-      <c r="F11" s="65">
+      <c r="F11" s="64">
         <f>D11*E11</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="12.75" customFormat="1" customHeight="1" s="43">
-      <c r="A12" s="62" t="inlineStr">
+    <row r="12" ht="12.75" customFormat="1" customHeight="1" s="44">
+      <c r="A12" s="57" t="inlineStr">
         <is>
           <t>1.2.</t>
         </is>
       </c>
-      <c r="B12" s="62" t="n"/>
-      <c r="C12" s="63" t="n"/>
-      <c r="D12" s="66" t="n"/>
-      <c r="E12" s="65" t="n"/>
-      <c r="F12" s="65">
+      <c r="B12" s="57" t="n"/>
+      <c r="C12" s="62" t="n"/>
+      <c r="D12" s="65" t="n"/>
+      <c r="E12" s="64" t="n"/>
+      <c r="F12" s="64">
         <f>D12*E12</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="12.75" customFormat="1" customHeight="1" s="43">
-      <c r="A13" s="62" t="n"/>
-      <c r="B13" s="67" t="inlineStr">
+    <row r="13" ht="12.75" customFormat="1" customHeight="1" s="44">
+      <c r="A13" s="57" t="n"/>
+      <c r="B13" s="66" t="inlineStr">
         <is>
           <t>Общо по т.1</t>
         </is>
       </c>
-      <c r="C13" s="58" t="n"/>
-      <c r="D13" s="58" t="n"/>
-      <c r="E13" s="58" t="n"/>
-      <c r="F13" s="68">
+      <c r="C13" s="59" t="n"/>
+      <c r="D13" s="59" t="n"/>
+      <c r="E13" s="59" t="n"/>
+      <c r="F13" s="64">
         <f>SUM(F11+F12)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="12.75" customFormat="1" customHeight="1" s="43">
-      <c r="A14" s="69" t="inlineStr">
+    <row r="14" ht="12.75" customFormat="1" customHeight="1" s="44">
+      <c r="A14" s="67" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="B14" s="70" t="inlineStr">
+      <c r="B14" s="68" t="inlineStr">
         <is>
           <t>Режийни разноски (10% от т.1)</t>
         </is>
       </c>
-      <c r="C14" s="58" t="n"/>
-      <c r="D14" s="58" t="n"/>
-      <c r="E14" s="58" t="n"/>
-      <c r="F14" s="71">
+      <c r="C14" s="59" t="n"/>
+      <c r="D14" s="59" t="n"/>
+      <c r="E14" s="59" t="n"/>
+      <c r="F14" s="69">
         <f>F13*0.1</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="12.75" customFormat="1" customHeight="1" s="43">
-      <c r="A15" s="69" t="inlineStr">
+    <row r="15" ht="12.75" customFormat="1" customHeight="1" s="44">
+      <c r="A15" s="67" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="B15" s="70" t="inlineStr">
+      <c r="B15" s="68" t="inlineStr">
         <is>
           <t>Разходи за консумативи/материали</t>
         </is>
       </c>
-      <c r="C15" s="58" t="n"/>
-      <c r="D15" s="58" t="n"/>
-      <c r="E15" s="58" t="n"/>
-      <c r="F15" s="71" t="n"/>
-    </row>
-    <row r="16" ht="12.75" customFormat="1" customHeight="1" s="43">
-      <c r="A16" s="61" t="inlineStr">
+      <c r="C15" s="59" t="n"/>
+      <c r="D15" s="59" t="n"/>
+      <c r="E15" s="59" t="n"/>
+      <c r="F15" s="69" t="n"/>
+    </row>
+    <row r="16" ht="12.75" customFormat="1" customHeight="1" s="44">
+      <c r="A16" s="58" t="inlineStr">
         <is>
           <t>3.1.</t>
         </is>
       </c>
-      <c r="B16" s="62" t="inlineStr">
+      <c r="B16" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve"> Отпечатване (формат А4, черно-бяло)</t>
         </is>
       </c>
-      <c r="C16" s="63" t="inlineStr">
+      <c r="C16" s="62" t="inlineStr">
         <is>
           <t>лист</t>
         </is>
       </c>
-      <c r="D16" s="64" t="n">
+      <c r="D16" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="65" t="n">
+      <c r="E16" s="64" t="n">
         <v>0.35</v>
       </c>
-      <c r="F16" s="65">
+      <c r="F16" s="64">
         <f>D16*E16</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="12.75" customFormat="1" customHeight="1" s="43">
-      <c r="A17" s="61" t="inlineStr">
+    <row r="17" ht="12.75" customFormat="1" customHeight="1" s="44">
+      <c r="A17" s="58" t="inlineStr">
         <is>
           <t>3.2.</t>
         </is>
       </c>
-      <c r="B17" s="62" t="inlineStr">
+      <c r="B17" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve"> Отпечатване (формат А4, цветно)</t>
         </is>
       </c>
-      <c r="C17" s="63" t="inlineStr">
+      <c r="C17" s="62" t="inlineStr">
         <is>
           <t>лист</t>
         </is>
       </c>
-      <c r="D17" s="64" t="n">
+      <c r="D17" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="65" t="n">
+      <c r="E17" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="65">
+      <c r="F17" s="64">
         <f>D17*E17</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="12.75" customFormat="1" customHeight="1" s="43">
-      <c r="A18" s="61" t="inlineStr">
+    <row r="18" ht="12.75" customFormat="1" customHeight="1" s="44">
+      <c r="A18" s="58" t="inlineStr">
         <is>
           <t>3.3.</t>
         </is>
       </c>
-      <c r="B18" s="62" t="inlineStr">
+      <c r="B18" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve"> Отпечатване (формат А3, черно-бяло)</t>
         </is>
       </c>
-      <c r="C18" s="63" t="inlineStr">
+      <c r="C18" s="62" t="inlineStr">
         <is>
           <t>лист</t>
         </is>
       </c>
-      <c r="D18" s="64" t="n">
+      <c r="D18" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="E18" s="65" t="n">
+      <c r="E18" s="64" t="n">
         <v>0.35</v>
       </c>
-      <c r="F18" s="65">
+      <c r="F18" s="64">
         <f>D18*E18</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="24.75" customFormat="1" customHeight="1" s="43">
-      <c r="A19" s="61" t="inlineStr">
+    <row r="19" ht="24.75" customFormat="1" customHeight="1" s="44">
+      <c r="A19" s="58" t="inlineStr">
         <is>
           <t>3.4.</t>
         </is>
       </c>
-      <c r="B19" s="61" t="inlineStr">
+      <c r="B19" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve"> Ръкавици, дезинфектант и маска за извършване на оглед на местопроизшествие</t>
         </is>
       </c>
-      <c r="C19" s="63" t="n"/>
-      <c r="D19" s="64" t="n">
+      <c r="C19" s="62" t="n"/>
+      <c r="D19" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="65" t="n">
+      <c r="E19" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="65">
+      <c r="F19" s="64">
         <f>D19*E19</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="12.75" customFormat="1" customHeight="1" s="43">
-      <c r="A20" s="61" t="inlineStr">
+    <row r="20" ht="12.75" customFormat="1" customHeight="1" s="44">
+      <c r="A20" s="58" t="inlineStr">
         <is>
           <t>3.4.</t>
         </is>
       </c>
-      <c r="B20" s="62" t="n"/>
-      <c r="C20" s="63" t="n"/>
-      <c r="D20" s="63" t="n"/>
-      <c r="E20" s="65" t="n"/>
-      <c r="F20" s="65" t="n"/>
-    </row>
-    <row r="21" ht="12.75" customFormat="1" customHeight="1" s="43">
-      <c r="A21" s="62" t="n"/>
-      <c r="B21" s="67" t="inlineStr">
+      <c r="B20" s="57" t="n"/>
+      <c r="C20" s="62" t="n"/>
+      <c r="D20" s="62" t="n"/>
+      <c r="E20" s="64" t="n"/>
+      <c r="F20" s="64" t="n"/>
+    </row>
+    <row r="21" ht="12.75" customFormat="1" customHeight="1" s="44">
+      <c r="A21" s="57" t="n"/>
+      <c r="B21" s="66" t="inlineStr">
         <is>
           <t>Общо по т.3</t>
         </is>
       </c>
-      <c r="C21" s="58" t="n"/>
-      <c r="D21" s="58" t="n"/>
-      <c r="E21" s="58" t="n"/>
-      <c r="F21" s="68">
+      <c r="C21" s="59" t="n"/>
+      <c r="D21" s="59" t="n"/>
+      <c r="E21" s="59" t="n"/>
+      <c r="F21" s="64">
         <f>SUM(F16:F20)</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="12.75" customFormat="1" customHeight="1" s="43">
-      <c r="A22" s="56" t="inlineStr">
+    <row r="22" ht="12.75" customFormat="1" customHeight="1" s="44">
+      <c r="A22" s="57" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="B22" s="57" t="inlineStr">
+      <c r="B22" s="58" t="inlineStr">
         <is>
           <t>* Добавки за:</t>
         </is>
       </c>
-      <c r="C22" s="58" t="n"/>
-      <c r="D22" s="58" t="n"/>
-      <c r="E22" s="59" t="n"/>
-      <c r="F22" s="68" t="n"/>
-    </row>
-    <row r="23" ht="12.75" customFormat="1" customHeight="1" s="43">
-      <c r="A23" s="62" t="n"/>
-      <c r="B23" s="61" t="inlineStr">
+      <c r="C22" s="59" t="n"/>
+      <c r="D22" s="59" t="n"/>
+      <c r="E22" s="60" t="n"/>
+      <c r="F22" s="64" t="n"/>
+    </row>
+    <row r="23" ht="12.75" customFormat="1" customHeight="1" s="44">
+      <c r="A23" s="57" t="n"/>
+      <c r="B23" s="58" t="inlineStr">
         <is>
           <t>Положен труд в почивни дни</t>
         </is>
       </c>
-      <c r="C23" s="63" t="inlineStr">
+      <c r="C23" s="62" t="inlineStr">
         <is>
           <t>час</t>
         </is>
       </c>
-      <c r="D23" s="66" t="n"/>
-      <c r="E23" s="65">
+      <c r="D23" s="65" t="n"/>
+      <c r="E23" s="64">
         <f>E11*0.5</f>
         <v/>
       </c>
-      <c r="F23" s="65">
+      <c r="F23" s="64">
         <f>D23*E23</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="25.5" customFormat="1" customHeight="1" s="43">
-      <c r="A24" s="62" t="n"/>
-      <c r="B24" s="61" t="inlineStr">
+    <row r="24" ht="12.75" customFormat="1" customHeight="1" s="44">
+      <c r="A24" s="57" t="n"/>
+      <c r="B24" s="58" t="inlineStr">
         <is>
           <t>Положен труд през дни на официални празници</t>
         </is>
       </c>
-      <c r="C24" s="63" t="inlineStr">
+      <c r="C24" s="62" t="inlineStr">
         <is>
           <t>час</t>
         </is>
       </c>
-      <c r="D24" s="66" t="n"/>
-      <c r="E24" s="65">
+      <c r="D24" s="65" t="n"/>
+      <c r="E24" s="64">
         <f>E11*1</f>
         <v/>
       </c>
-      <c r="F24" s="65">
+      <c r="F24" s="64">
         <f>D24*E24</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="25.5" customFormat="1" customHeight="1" s="43">
-      <c r="A25" s="62" t="n"/>
-      <c r="B25" s="61" t="inlineStr">
+    <row r="25" ht="12.75" customFormat="1" customHeight="1" s="44">
+      <c r="A25" s="57" t="n"/>
+      <c r="B25" s="58" t="inlineStr">
         <is>
           <t>За особено сложна и специфична експертиза</t>
         </is>
       </c>
-      <c r="C25" s="63" t="n"/>
-      <c r="D25" s="66" t="n"/>
-      <c r="E25" s="72" t="n"/>
-      <c r="F25" s="65">
+      <c r="C25" s="62" t="n"/>
+      <c r="D25" s="65" t="n"/>
+      <c r="E25" s="70" t="n"/>
+      <c r="F25" s="64">
         <f>D25*E25</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="12.75" customFormat="1" customHeight="1" s="43">
-      <c r="A26" s="62" t="n"/>
-      <c r="B26" s="67" t="inlineStr">
+    <row r="26" ht="12.75" customFormat="1" customHeight="1" s="44">
+      <c r="A26" s="57" t="n"/>
+      <c r="B26" s="66" t="inlineStr">
         <is>
           <t>Общо по т.4</t>
         </is>
       </c>
-      <c r="C26" s="58" t="n"/>
-      <c r="D26" s="58" t="n"/>
-      <c r="E26" s="58" t="n"/>
-      <c r="F26" s="68">
+      <c r="C26" s="59" t="n"/>
+      <c r="D26" s="59" t="n"/>
+      <c r="E26" s="59" t="n"/>
+      <c r="F26" s="64">
         <f>SUM(F23+F24+F25)</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customFormat="1" customHeight="1" s="43">
-      <c r="A27" s="56" t="inlineStr">
+    <row r="27" ht="15" customFormat="1" customHeight="1" s="44">
+      <c r="A27" s="57" t="inlineStr">
         <is>
           <t>5.</t>
         </is>
       </c>
-      <c r="B27" s="57" t="inlineStr">
+      <c r="B27" s="58" t="inlineStr">
         <is>
           <t>ОБЩА СТОЙНОСТ 1+2+3+4:</t>
         </is>
       </c>
-      <c r="C27" s="58" t="n"/>
-      <c r="D27" s="58" t="n"/>
-      <c r="E27" s="59" t="n"/>
-      <c r="F27" s="68">
+      <c r="C27" s="59" t="n"/>
+      <c r="D27" s="59" t="n"/>
+      <c r="E27" s="60" t="n"/>
+      <c r="F27" s="64">
         <f>SUM(F13+F14+F21+F26)</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="12.75" customHeight="1" s="51">
-      <c r="A28" s="73" t="inlineStr">
+    <row r="28" ht="12.75" customHeight="1" s="52">
+      <c r="A28" s="71" t="inlineStr">
         <is>
           <t xml:space="preserve">          * Добавките по т. 4 се калкулират на база на разходите за труд по т. 1.</t>
         </is>
       </c>
-      <c r="B28" s="74" t="n"/>
-      <c r="C28" s="74" t="n"/>
-      <c r="D28" s="74" t="n"/>
-      <c r="E28" s="74" t="n"/>
-      <c r="F28" s="74" t="n"/>
-    </row>
-    <row r="29" ht="7.5" customHeight="1" s="51">
-      <c r="A29" s="75" t="n"/>
-    </row>
-    <row r="30" ht="30" customHeight="1" s="51">
-      <c r="A30" s="76" t="inlineStr">
+      <c r="B28" s="72" t="n"/>
+      <c r="C28" s="72" t="n"/>
+      <c r="D28" s="72" t="n"/>
+      <c r="E28" s="72" t="n"/>
+      <c r="F28" s="72" t="n"/>
+    </row>
+    <row r="29" ht="7.5" customHeight="1" s="52">
+      <c r="A29" s="73" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1" s="52">
+      <c r="A30" s="74" t="inlineStr">
         <is>
           <t xml:space="preserve">         Обща стойност (словом): ……………………………………….……………………………..… …………………………………………………………………………………………………………….</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1" s="51">
-      <c r="A31" s="77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         Сумата да бъде преведена по сметка с IBAN № BG96UBBS80023112509310, при банка ОББ-АД – клон Плевен в 30 дневен срок от датата на приемането на експертизата.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="45" customHeight="1" s="51">
-      <c r="A32" s="77" t="inlineStr">
+    <row r="31" ht="30" customHeight="1" s="52">
+      <c r="A31" s="75" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <charset val="204"/>
+              <family val="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">         Сумата да бъде преведена по сметка с IBAN № </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <charset val="204"/>
+              <family val="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>BG96UBBS80023112509310</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <charset val="204"/>
+              <family val="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">, при банка </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <charset val="204"/>
+              <family val="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>ОББ-АД – клон Плевен</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <charset val="204"/>
+              <family val="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> в 30 дневен срок от датата на приемането на експертизата.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="45" customHeight="1" s="52">
+      <c r="A32" s="75" t="inlineStr">
         <is>
           <t xml:space="preserve">         Моля, при заплащане на задълженията Ви към МВР за изготвени експертизи, при иницииране на платежен документ, в основанието да се посочва рег. № на сметката и № на протокола от изследването.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="7.5" customHeight="1" s="51">
-      <c r="A33" s="78" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="51">
-      <c r="A34" s="79" t="inlineStr">
+    <row r="33" ht="7.5" customHeight="1" s="52">
+      <c r="A33" s="76" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="52">
+      <c r="A34" s="77" t="inlineStr">
         <is>
           <t>Отп:  в 4 екз.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="12.75" customHeight="1" s="51">
-      <c r="A35" s="48" t="inlineStr">
+    <row r="35" ht="12.75" customHeight="1" s="52">
+      <c r="A35" s="49" t="inlineStr">
         <is>
           <t>Екз.№1 – Деловодство</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="12.75" customHeight="1" s="51">
-      <c r="A36" s="48" t="inlineStr">
+    <row r="36" ht="12.75" customHeight="1" s="52">
+      <c r="A36" s="49" t="inlineStr">
         <is>
           <t>Екз.№2 – Възложител</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="12.75" customHeight="1" s="51">
-      <c r="A37" s="48" t="inlineStr">
-        <is>
-          <t>Екз.№3 – Възложител (без приложение)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="12.75" customHeight="1" s="51">
-      <c r="A38" s="48" t="inlineStr">
-        <is>
-          <t>Екз.№4 – ФО (без приложение)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="7.5" customHeight="1" s="51">
-      <c r="A39" s="78" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="51">
-      <c r="A40" s="78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Приложение: Експертиза – 1 бр.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="13.5" customHeight="1" s="51">
-      <c r="A41" s="78" t="n"/>
-      <c r="B41" s="78" t="n"/>
-      <c r="C41" s="78" t="n"/>
-      <c r="D41" s="78" t="n"/>
-      <c r="E41" s="78" t="n"/>
-      <c r="F41" s="78" t="n"/>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="51">
-      <c r="A42" s="80" t="inlineStr">
+    <row r="37" ht="12.75" customHeight="1" s="52">
+      <c r="A37" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <charset val="204"/>
+              <family val="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Екз.№3 – Възложител </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <charset val="204"/>
+              <family val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(без приложение)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="12.75" customHeight="1" s="52">
+      <c r="A38" s="49" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <charset val="204"/>
+              <family val="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Екз.№4 – ФО </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <charset val="204"/>
+              <family val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(без приложение)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="7.5" customHeight="1" s="52">
+      <c r="A39" s="76" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="52">
+      <c r="A40" s="76" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <charset val="204"/>
+              <family val="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Приложение:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <charset val="204"/>
+              <family val="1"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> Експертиза – 1 бр.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="13.5" customHeight="1" s="52">
+      <c r="A41" s="76" t="n"/>
+      <c r="B41" s="76" t="n"/>
+      <c r="C41" s="76" t="n"/>
+      <c r="D41" s="76" t="n"/>
+      <c r="E41" s="76" t="n"/>
+      <c r="F41" s="76" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="52">
+      <c r="A42" s="78" t="inlineStr">
         <is>
           <t>Изготвил:</t>
         </is>
       </c>
-      <c r="C42" s="81" t="n"/>
-      <c r="D42" s="78" t="inlineStr">
+      <c r="C42" s="79" t="n"/>
+      <c r="D42" s="76" t="inlineStr">
         <is>
           <t>ДИРЕКТОР:</t>
         </is>
       </c>
-      <c r="E42" s="78" t="n"/>
-      <c r="F42" s="78" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="51">
-      <c r="A43" s="82" t="inlineStr">
+      <c r="E42" s="76" t="n"/>
+      <c r="F42" s="76" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="52">
+      <c r="A43" s="80" t="inlineStr">
         <is>
           <t>/ инспектор Х.Ххххххххххх /</t>
         </is>
       </c>
-      <c r="C43" s="81" t="n"/>
-      <c r="D43" s="78" t="inlineStr">
+      <c r="C43" s="79" t="n"/>
+      <c r="D43" s="76" t="inlineStr">
         <is>
           <t>РДПБЗН – ПЛЕВЕН</t>
         </is>
       </c>
-      <c r="E43" s="78" t="n"/>
-      <c r="F43" s="78" t="n"/>
-    </row>
-    <row r="44" ht="15" customFormat="1" customHeight="1" s="43">
-      <c r="A44" s="80" t="inlineStr">
+      <c r="E43" s="76" t="n"/>
+      <c r="F43" s="76" t="n"/>
+    </row>
+    <row r="44" ht="15" customFormat="1" customHeight="1" s="44">
+      <c r="A44" s="78" t="inlineStr">
         <is>
           <t>гр. Плевен</t>
         </is>
       </c>
-      <c r="C44" s="83" t="n"/>
-      <c r="D44" s="48" t="inlineStr">
+      <c r="C44" s="81" t="n"/>
+      <c r="D44" s="49" t="inlineStr">
         <is>
           <t>[ЗВАНИЕ]</t>
         </is>
       </c>
-      <c r="E44" s="48" t="n"/>
-      <c r="F44" s="48" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="51">
-      <c r="A45" s="80" t="inlineStr">
+      <c r="E44" s="49" t="n"/>
+      <c r="F44" s="49" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="52">
+      <c r="A45" s="78" t="inlineStr">
         <is>
           <t>……....20…..г.</t>
         </is>
       </c>
-      <c r="C45" s="81" t="n"/>
-      <c r="D45" s="84" t="inlineStr">
+      <c r="C45" s="79" t="n"/>
+      <c r="D45" s="82" t="inlineStr">
         <is>
           <t xml:space="preserve">   [Име Фамилия]</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="51">
-      <c r="A46" s="84" t="n"/>
-      <c r="C46" s="81" t="n"/>
-      <c r="D46" s="84" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="51">
-      <c r="A47" s="80" t="n"/>
-      <c r="C47" s="81" t="n"/>
-      <c r="D47" s="84" t="n"/>
+    <row r="46" ht="15" customHeight="1" s="52">
+      <c r="A46" s="82" t="n"/>
+      <c r="C46" s="79" t="n"/>
+      <c r="D46" s="82" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="52">
+      <c r="A47" s="78" t="n"/>
+      <c r="C47" s="79" t="n"/>
+      <c r="D47" s="82" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="37">
@@ -1337,6 +1425,5 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.39375" right="0.39375" top="0.39375" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/plugins/fire-service/skills/eptz/assets/smetka_template.xlsx
+++ b/plugins/fire-service/skills/eptz/assets/smetka_template.xlsx
@@ -203,7 +203,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -365,24 +365,30 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -394,16 +400,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -427,6 +436,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom" wrapText="1"/>
@@ -795,51 +807,51 @@
       <c r="F10" s="61" t="n"/>
     </row>
     <row r="11" ht="12.75" customFormat="1" customHeight="1" s="44">
-      <c r="A11" s="58" t="inlineStr">
+      <c r="A11" s="62" t="inlineStr">
         <is>
           <t>1.1.</t>
         </is>
       </c>
-      <c r="B11" s="57" t="inlineStr">
+      <c r="B11" s="63" t="inlineStr">
         <is>
           <t>Инспектор VI - IV степен</t>
         </is>
       </c>
-      <c r="C11" s="62" t="inlineStr">
+      <c r="C11" s="64" t="inlineStr">
         <is>
           <t>час</t>
         </is>
       </c>
-      <c r="D11" s="63" t="n">
+      <c r="D11" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="64">
+      <c r="E11" s="66">
         <f>3.5%*620.2</f>
         <v/>
       </c>
-      <c r="F11" s="64">
+      <c r="F11" s="66">
         <f>D11*E11</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="12.75" customFormat="1" customHeight="1" s="44">
-      <c r="A12" s="57" t="inlineStr">
+      <c r="A12" s="63" t="inlineStr">
         <is>
           <t>1.2.</t>
         </is>
       </c>
-      <c r="B12" s="57" t="n"/>
-      <c r="C12" s="62" t="n"/>
-      <c r="D12" s="65" t="n"/>
-      <c r="E12" s="64" t="n"/>
-      <c r="F12" s="64">
+      <c r="B12" s="63" t="n"/>
+      <c r="C12" s="64" t="n"/>
+      <c r="D12" s="67" t="n"/>
+      <c r="E12" s="66" t="n"/>
+      <c r="F12" s="66">
         <f>D12*E12</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="12.75" customFormat="1" customHeight="1" s="44">
-      <c r="A13" s="57" t="n"/>
-      <c r="B13" s="66" t="inlineStr">
+      <c r="A13" s="63" t="n"/>
+      <c r="B13" s="68" t="inlineStr">
         <is>
           <t>Общо по т.1</t>
         </is>
@@ -847,18 +859,18 @@
       <c r="C13" s="59" t="n"/>
       <c r="D13" s="59" t="n"/>
       <c r="E13" s="59" t="n"/>
-      <c r="F13" s="64">
+      <c r="F13" s="69">
         <f>SUM(F11+F12)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="12.75" customFormat="1" customHeight="1" s="44">
-      <c r="A14" s="67" t="inlineStr">
+      <c r="A14" s="70" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="B14" s="68" t="inlineStr">
+      <c r="B14" s="71" t="inlineStr">
         <is>
           <t>Режийни разноски (10% от т.1)</t>
         </is>
@@ -866,18 +878,18 @@
       <c r="C14" s="59" t="n"/>
       <c r="D14" s="59" t="n"/>
       <c r="E14" s="59" t="n"/>
-      <c r="F14" s="69">
+      <c r="F14" s="72">
         <f>F13*0.1</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="12.75" customFormat="1" customHeight="1" s="44">
-      <c r="A15" s="67" t="inlineStr">
+      <c r="A15" s="70" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="B15" s="68" t="inlineStr">
+      <c r="B15" s="71" t="inlineStr">
         <is>
           <t>Разходи за консумативи/материали</t>
         </is>
@@ -885,127 +897,127 @@
       <c r="C15" s="59" t="n"/>
       <c r="D15" s="59" t="n"/>
       <c r="E15" s="59" t="n"/>
-      <c r="F15" s="69" t="n"/>
+      <c r="F15" s="72" t="n"/>
     </row>
     <row r="16" ht="12.75" customFormat="1" customHeight="1" s="44">
-      <c r="A16" s="58" t="inlineStr">
+      <c r="A16" s="62" t="inlineStr">
         <is>
           <t>3.1.</t>
         </is>
       </c>
-      <c r="B16" s="57" t="inlineStr">
+      <c r="B16" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve"> Отпечатване (формат А4, черно-бяло)</t>
         </is>
       </c>
-      <c r="C16" s="62" t="inlineStr">
+      <c r="C16" s="64" t="inlineStr">
         <is>
           <t>лист</t>
         </is>
       </c>
-      <c r="D16" s="63" t="n">
+      <c r="D16" s="65" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="64" t="n">
+      <c r="E16" s="66" t="n">
         <v>0.35</v>
       </c>
-      <c r="F16" s="64">
+      <c r="F16" s="66">
         <f>D16*E16</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="12.75" customFormat="1" customHeight="1" s="44">
-      <c r="A17" s="58" t="inlineStr">
+      <c r="A17" s="62" t="inlineStr">
         <is>
           <t>3.2.</t>
         </is>
       </c>
-      <c r="B17" s="57" t="inlineStr">
+      <c r="B17" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve"> Отпечатване (формат А4, цветно)</t>
         </is>
       </c>
-      <c r="C17" s="62" t="inlineStr">
+      <c r="C17" s="64" t="inlineStr">
         <is>
           <t>лист</t>
         </is>
       </c>
-      <c r="D17" s="63" t="n">
+      <c r="D17" s="65" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="64" t="n">
+      <c r="E17" s="66" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="64">
+      <c r="F17" s="66">
         <f>D17*E17</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="12.75" customFormat="1" customHeight="1" s="44">
-      <c r="A18" s="58" t="inlineStr">
+      <c r="A18" s="62" t="inlineStr">
         <is>
           <t>3.3.</t>
         </is>
       </c>
-      <c r="B18" s="57" t="inlineStr">
+      <c r="B18" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve"> Отпечатване (формат А3, черно-бяло)</t>
         </is>
       </c>
-      <c r="C18" s="62" t="inlineStr">
+      <c r="C18" s="64" t="inlineStr">
         <is>
           <t>лист</t>
         </is>
       </c>
-      <c r="D18" s="63" t="n">
+      <c r="D18" s="65" t="n">
         <v>2</v>
       </c>
-      <c r="E18" s="64" t="n">
+      <c r="E18" s="66" t="n">
         <v>0.35</v>
       </c>
-      <c r="F18" s="64">
+      <c r="F18" s="66">
         <f>D18*E18</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="24.75" customFormat="1" customHeight="1" s="44">
-      <c r="A19" s="58" t="inlineStr">
+      <c r="A19" s="62" t="inlineStr">
         <is>
           <t>3.4.</t>
         </is>
       </c>
-      <c r="B19" s="58" t="inlineStr">
+      <c r="B19" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve"> Ръкавици, дезинфектант и маска за извършване на оглед на местопроизшествие</t>
         </is>
       </c>
-      <c r="C19" s="62" t="n"/>
-      <c r="D19" s="63" t="n">
+      <c r="C19" s="64" t="n"/>
+      <c r="D19" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="64" t="n">
+      <c r="E19" s="66" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="64">
+      <c r="F19" s="66">
         <f>D19*E19</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="12.75" customFormat="1" customHeight="1" s="44">
-      <c r="A20" s="58" t="inlineStr">
+      <c r="A20" s="62" t="inlineStr">
         <is>
           <t>3.4.</t>
         </is>
       </c>
-      <c r="B20" s="57" t="n"/>
-      <c r="C20" s="62" t="n"/>
-      <c r="D20" s="62" t="n"/>
-      <c r="E20" s="64" t="n"/>
-      <c r="F20" s="64" t="n"/>
+      <c r="B20" s="63" t="n"/>
+      <c r="C20" s="64" t="n"/>
+      <c r="D20" s="64" t="n"/>
+      <c r="E20" s="66" t="n"/>
+      <c r="F20" s="66" t="n"/>
     </row>
     <row r="21" ht="12.75" customFormat="1" customHeight="1" s="44">
-      <c r="A21" s="57" t="n"/>
-      <c r="B21" s="66" t="inlineStr">
+      <c r="A21" s="63" t="n"/>
+      <c r="B21" s="68" t="inlineStr">
         <is>
           <t>Общо по т.3</t>
         </is>
@@ -1013,7 +1025,7 @@
       <c r="C21" s="59" t="n"/>
       <c r="D21" s="59" t="n"/>
       <c r="E21" s="59" t="n"/>
-      <c r="F21" s="64">
+      <c r="F21" s="69">
         <f>SUM(F16:F20)</f>
         <v/>
       </c>
@@ -1032,70 +1044,70 @@
       <c r="C22" s="59" t="n"/>
       <c r="D22" s="59" t="n"/>
       <c r="E22" s="60" t="n"/>
-      <c r="F22" s="64" t="n"/>
+      <c r="F22" s="69" t="n"/>
     </row>
     <row r="23" ht="12.75" customFormat="1" customHeight="1" s="44">
-      <c r="A23" s="57" t="n"/>
-      <c r="B23" s="58" t="inlineStr">
+      <c r="A23" s="63" t="n"/>
+      <c r="B23" s="62" t="inlineStr">
         <is>
           <t>Положен труд в почивни дни</t>
         </is>
       </c>
-      <c r="C23" s="62" t="inlineStr">
+      <c r="C23" s="64" t="inlineStr">
         <is>
           <t>час</t>
         </is>
       </c>
-      <c r="D23" s="65" t="n"/>
-      <c r="E23" s="64">
+      <c r="D23" s="67" t="n"/>
+      <c r="E23" s="66">
         <f>E11*0.5</f>
         <v/>
       </c>
-      <c r="F23" s="64">
+      <c r="F23" s="66">
         <f>D23*E23</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="12.75" customFormat="1" customHeight="1" s="44">
-      <c r="A24" s="57" t="n"/>
-      <c r="B24" s="58" t="inlineStr">
+      <c r="A24" s="63" t="n"/>
+      <c r="B24" s="62" t="inlineStr">
         <is>
           <t>Положен труд през дни на официални празници</t>
         </is>
       </c>
-      <c r="C24" s="62" t="inlineStr">
+      <c r="C24" s="64" t="inlineStr">
         <is>
           <t>час</t>
         </is>
       </c>
-      <c r="D24" s="65" t="n"/>
-      <c r="E24" s="64">
+      <c r="D24" s="67" t="n"/>
+      <c r="E24" s="66">
         <f>E11*1</f>
         <v/>
       </c>
-      <c r="F24" s="64">
+      <c r="F24" s="66">
         <f>D24*E24</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="12.75" customFormat="1" customHeight="1" s="44">
-      <c r="A25" s="57" t="n"/>
-      <c r="B25" s="58" t="inlineStr">
+      <c r="A25" s="63" t="n"/>
+      <c r="B25" s="62" t="inlineStr">
         <is>
           <t>За особено сложна и специфична експертиза</t>
         </is>
       </c>
-      <c r="C25" s="62" t="n"/>
-      <c r="D25" s="65" t="n"/>
-      <c r="E25" s="70" t="n"/>
-      <c r="F25" s="64">
+      <c r="C25" s="64" t="n"/>
+      <c r="D25" s="67" t="n"/>
+      <c r="E25" s="73" t="n"/>
+      <c r="F25" s="66">
         <f>D25*E25</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="12.75" customFormat="1" customHeight="1" s="44">
-      <c r="A26" s="57" t="n"/>
-      <c r="B26" s="66" t="inlineStr">
+      <c r="A26" s="63" t="n"/>
+      <c r="B26" s="68" t="inlineStr">
         <is>
           <t>Общо по т.4</t>
         </is>
@@ -1103,7 +1115,7 @@
       <c r="C26" s="59" t="n"/>
       <c r="D26" s="59" t="n"/>
       <c r="E26" s="59" t="n"/>
-      <c r="F26" s="64">
+      <c r="F26" s="69">
         <f>SUM(F23+F24+F25)</f>
         <v/>
       </c>
@@ -1122,35 +1134,35 @@
       <c r="C27" s="59" t="n"/>
       <c r="D27" s="59" t="n"/>
       <c r="E27" s="60" t="n"/>
-      <c r="F27" s="64">
+      <c r="F27" s="69">
         <f>SUM(F13+F14+F21+F26)</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="12.75" customHeight="1" s="52">
-      <c r="A28" s="71" t="inlineStr">
+      <c r="A28" s="74" t="inlineStr">
         <is>
           <t xml:space="preserve">          * Добавките по т. 4 се калкулират на база на разходите за труд по т. 1.</t>
         </is>
       </c>
-      <c r="B28" s="72" t="n"/>
-      <c r="C28" s="72" t="n"/>
-      <c r="D28" s="72" t="n"/>
-      <c r="E28" s="72" t="n"/>
-      <c r="F28" s="72" t="n"/>
+      <c r="B28" s="75" t="n"/>
+      <c r="C28" s="75" t="n"/>
+      <c r="D28" s="75" t="n"/>
+      <c r="E28" s="75" t="n"/>
+      <c r="F28" s="75" t="n"/>
     </row>
     <row r="29" ht="7.5" customHeight="1" s="52">
-      <c r="A29" s="73" t="n"/>
+      <c r="A29" s="76" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1" s="52">
-      <c r="A30" s="74" t="inlineStr">
+      <c r="A30" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">         Обща стойност (словом): ……………………………………….……………………………..… …………………………………………………………………………………………………………….</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" s="52">
-      <c r="A31" s="75" t="inlineStr">
+      <c r="A31" s="78" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1166,6 +1178,7 @@
               <rFont val="Times New Roman"/>
               <charset val="204"/>
               <family val="1"/>
+              <b val="1"/>
               <sz val="12"/>
             </rPr>
             <t>BG96UBBS80023112509310</t>
@@ -1184,6 +1197,7 @@
               <rFont val="Times New Roman"/>
               <charset val="204"/>
               <family val="1"/>
+              <b val="1"/>
               <sz val="12"/>
             </rPr>
             <t>ОББ-АД – клон Плевен</t>
@@ -1201,17 +1215,17 @@
       </c>
     </row>
     <row r="32" ht="45" customHeight="1" s="52">
-      <c r="A32" s="75" t="inlineStr">
+      <c r="A32" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">         Моля, при заплащане на задълженията Ви към МВР за изготвени експертизи, при иницииране на платежен документ, в основанието да се посочва рег. № на сметката и № на протокола от изследването.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="7.5" customHeight="1" s="52">
-      <c r="A33" s="76" t="n"/>
+      <c r="A33" s="79" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1" s="52">
-      <c r="A34" s="77" t="inlineStr">
+      <c r="A34" s="80" t="inlineStr">
         <is>
           <t>Отп:  в 4 екз.</t>
         </is>
@@ -1280,16 +1294,17 @@
       </c>
     </row>
     <row r="39" ht="7.5" customHeight="1" s="52">
-      <c r="A39" s="76" t="n"/>
+      <c r="A39" s="79" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="52">
-      <c r="A40" s="76" t="inlineStr">
+      <c r="A40" s="81" t="inlineStr">
         <is>
           <r>
             <rPr>
               <rFont val="Times New Roman"/>
               <charset val="204"/>
               <family val="1"/>
+              <b val="1"/>
               <sz val="12"/>
             </rPr>
             <t>Приложение:</t>
@@ -1307,50 +1322,50 @@
       </c>
     </row>
     <row r="41" ht="13.5" customHeight="1" s="52">
-      <c r="A41" s="76" t="n"/>
-      <c r="B41" s="76" t="n"/>
-      <c r="C41" s="76" t="n"/>
-      <c r="D41" s="76" t="n"/>
-      <c r="E41" s="76" t="n"/>
-      <c r="F41" s="76" t="n"/>
+      <c r="A41" s="79" t="n"/>
+      <c r="B41" s="79" t="n"/>
+      <c r="C41" s="79" t="n"/>
+      <c r="D41" s="79" t="n"/>
+      <c r="E41" s="79" t="n"/>
+      <c r="F41" s="79" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1" s="52">
-      <c r="A42" s="78" t="inlineStr">
+      <c r="A42" s="82" t="inlineStr">
         <is>
           <t>Изготвил:</t>
         </is>
       </c>
-      <c r="C42" s="79" t="n"/>
-      <c r="D42" s="76" t="inlineStr">
+      <c r="C42" s="83" t="n"/>
+      <c r="D42" s="79" t="inlineStr">
         <is>
           <t>ДИРЕКТОР:</t>
         </is>
       </c>
-      <c r="E42" s="76" t="n"/>
-      <c r="F42" s="76" t="n"/>
+      <c r="E42" s="79" t="n"/>
+      <c r="F42" s="79" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1" s="52">
-      <c r="A43" s="80" t="inlineStr">
+      <c r="A43" s="84" t="inlineStr">
         <is>
           <t>/ инспектор Х.Ххххххххххх /</t>
         </is>
       </c>
-      <c r="C43" s="79" t="n"/>
-      <c r="D43" s="76" t="inlineStr">
+      <c r="C43" s="83" t="n"/>
+      <c r="D43" s="79" t="inlineStr">
         <is>
           <t>РДПБЗН – ПЛЕВЕН</t>
         </is>
       </c>
-      <c r="E43" s="76" t="n"/>
-      <c r="F43" s="76" t="n"/>
+      <c r="E43" s="79" t="n"/>
+      <c r="F43" s="79" t="n"/>
     </row>
     <row r="44" ht="15" customFormat="1" customHeight="1" s="44">
-      <c r="A44" s="78" t="inlineStr">
+      <c r="A44" s="82" t="inlineStr">
         <is>
           <t>гр. Плевен</t>
         </is>
       </c>
-      <c r="C44" s="81" t="n"/>
+      <c r="C44" s="85" t="n"/>
       <c r="D44" s="49" t="inlineStr">
         <is>
           <t>[ЗВАНИЕ]</t>
@@ -1360,27 +1375,27 @@
       <c r="F44" s="49" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1" s="52">
-      <c r="A45" s="78" t="inlineStr">
+      <c r="A45" s="82" t="inlineStr">
         <is>
           <t>……....20…..г.</t>
         </is>
       </c>
-      <c r="C45" s="79" t="n"/>
-      <c r="D45" s="82" t="inlineStr">
+      <c r="C45" s="83" t="n"/>
+      <c r="D45" s="86" t="inlineStr">
         <is>
           <t xml:space="preserve">   [Име Фамилия]</t>
         </is>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="52">
-      <c r="A46" s="82" t="n"/>
-      <c r="C46" s="79" t="n"/>
-      <c r="D46" s="82" t="n"/>
+      <c r="A46" s="86" t="n"/>
+      <c r="C46" s="83" t="n"/>
+      <c r="D46" s="86" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1" s="52">
-      <c r="A47" s="78" t="n"/>
-      <c r="C47" s="79" t="n"/>
-      <c r="D47" s="82" t="n"/>
+      <c r="A47" s="82" t="n"/>
+      <c r="C47" s="83" t="n"/>
+      <c r="D47" s="86" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="37">
